--- a/data/seed/portfolio/L-2025-1139/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-1139/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -560,38 +560,38 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>2551000</v>
+        <v>2784000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4868 от 01.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №186/26 от 01.07.2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,23 +599,23 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>133212000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>3289000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №286/26 от 01.07.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №178/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -642,38 +642,38 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>6808000</v>
+        <v>1935000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish Materiallari MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>215886707</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000749970064001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №286/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №280/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -683,38 +683,38 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>1522000</v>
+        <v>7245000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №280/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №275/26 от 03.07.2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -724,31 +724,31 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>5488000</v>
+        <v>9743000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Olmaliq Poligraf XK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>219799595</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000788779386001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №275/26 от 03.07.2026</t>
+          <t>Оплата по счет-фактуре №5136 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -765,26 +765,26 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>19078000</v>
+        <v>8930000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -806,31 +806,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>3239000</v>
+        <v>8034000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №168/26, НДС 12%</t>
+          <t>Оплата по с/ №2622 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -847,31 +847,31 @@
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>2661000</v>
+        <v>2026000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8475 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №168/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -886,33 +886,33 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>1844000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>3095000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5639 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №5101</t>
         </is>
       </c>
     </row>
@@ -928,39 +928,34 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4481000</v>
+        <v>8723000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>209992502</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №258/26</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №6378</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,35 +963,40 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>8723000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>2539000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Afrosiyob Non MChJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>338086761</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000188311188001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №1752</t>
+          <t>Предоплата за товар по дог. №191/26 от 08.07.2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1010,17 +1010,17 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari XK</t>
+          <t>Chust Qurilish MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>249052323</t>
+          <t>388102280</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000327831328001</t>
+          <t>20208000824216117001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1030,14 +1030,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Арендная плата за июль 2026 г. по договору №57/25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1047,21 +1047,21 @@
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>2777000</v>
+        <v>5331000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Bahor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>388670757</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000997006490001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1071,14 +1071,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №3396 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за продукцию по договору №162/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1086,23 +1086,23 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>2932000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>4491000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1112,14 +1112,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №8/26 от 09.07.2026, НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8880 ОТ 13.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1129,31 +1129,31 @@
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>2291000</v>
+        <v>2277000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish Materiallari MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>215886707</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000749970064001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №162/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №229/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1170,31 +1170,31 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>29750000</v>
+        <v>1738000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8880 ОТ 13.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №6547 13.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1209,40 +1209,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>11422000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>4302000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish Materiallari MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>215886707</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000749970064001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2268 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №229/26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1252,38 +1252,38 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>1894000</v>
+        <v>5700000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1815 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №9543 от 14.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1293,38 +1293,38 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>1608000</v>
+        <v>3930000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №41 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по с/ф №3207 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1333,39 +1333,39 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2998000</v>
+        <v>1189000</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №275/26</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1373,33 +1373,33 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>9967000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>1189000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9543 от 14.07.2026, в т.ч. НДС 12%</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
     </row>
@@ -1414,23 +1414,18 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>7121000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>13700000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>311312733</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-1139)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>16307000397310639417</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1440,14 +1435,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3207 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2025-1139 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1455,35 +1450,40 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>13700000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>12510000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-1139)</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>16307000397310639417</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-1139 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за продукцию по договору №153/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1493,38 +1493,38 @@
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>4261000</v>
+        <v>4109000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №153/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6380 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1532,40 +1532,40 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>1189000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>2155000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Shartnoma №265/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1573,40 +1573,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>1189000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>2126000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Предоплата за товар по договору №249/26 от 20.07.2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1615,22 +1615,22 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3506000</v>
+        <v>10153000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №289/26</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №151/26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1657,38 +1657,38 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>18253000</v>
+        <v>4787000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Shartnoma №242/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по дог. №68/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1698,38 +1698,38 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>8845000</v>
+        <v>4017000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №266/26 от 20.07.2026</t>
+          <t>Оплата за товар по счет-фактуре №6563 от 22.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1739,38 +1739,38 @@
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>6548000</v>
+        <v>3581000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Shodlik Mebel MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>335501999</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000855225308001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №249/26 от 20.07.2026</t>
+          <t>Оплата за продукцию по договору №219/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1778,40 +1778,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>2820000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>2534000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6380 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,40 +1819,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>1593000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>4466000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Shartnoma №265/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по дог. №200/26 от 22.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1860,40 +1860,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>2555000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>23893000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Agro XK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>383301382</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000360420837001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>Оплата по счет-фактуре №6385 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1902,39 +1902,39 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>5763000</v>
+        <v>982000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000883060321001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №280/26 от 21.07.2026, НДС 12%</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1942,40 +1942,40 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>24072000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>2203000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>257402187</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000921132739001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5489</t>
+          <t>Mahsulot uchun to'lov, shartnoma №268/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1983,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>3970000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>14134000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish Materiallari MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>215886707</t>
+          <t>397943825</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000749970064001</t>
+          <t>20208000533605331001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №19 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №807</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2026,38 +2026,38 @@
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>2354000</v>
+        <v>32382000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sharq Plastik MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>267355019</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000978552253001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №219/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №3320 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2067,38 +2067,38 @@
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>2407000</v>
+        <v>16215000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz XK</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>386833013</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000273604208001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6385 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1105 27.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2108,38 +2108,38 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>9270000</v>
+        <v>5405000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №268/26, QQS 12%</t>
+          <t>Mahsulot ucun to'lov, shartn. №226/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2149,38 +2149,38 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>3404000</v>
+        <v>2046000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Bahor Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>390855112</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000036327623001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4105 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7450</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2189,22 +2189,22 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>982000</v>
+        <v>3278000</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>397943825</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000001784401001</t>
+          <t>20208000533605331001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
+          <t>Оплата за товары согласно с/ф №4168</t>
         </is>
       </c>
     </row>
@@ -2229,23 +2229,23 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>12724000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>19844000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>397943825</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000533605331001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1105 27.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №145/26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,40 +2270,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>2483000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>22861000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish Materiallari MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>215886707</t>
+          <t>397943825</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000749970064001</t>
+          <t>20208000533605331001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №185/26 ОТ 28.07.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №27/26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2313,31 +2313,31 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>2142000</v>
+        <v>10265000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7438 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №8320 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -2354,26 +2354,26 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>6745000</v>
+        <v>2071000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2385,7 +2385,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>1885000</v>
+        <v>6819000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Jizzax Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>365230045</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000758642853001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8320 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8113 30.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2436,21 +2436,21 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>10253000</v>
+        <v>6573000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Navro'z Tur Servis XK</t>
+          <t>Bahor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>315057106</t>
+          <t>388670757</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000884317090001</t>
+          <t>20208000997006490001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №1/26 от 30.07.2026</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №167/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2475,33 +2475,28 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>2941000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>215886707</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000749970064001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №167/26, НДС 12%</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
     </row>
@@ -2517,34 +2512,39 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>300000</v>
+        <v>99951000</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Marg'ilon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за транспортные услуги по договору №99/26</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2552,33 +2552,33 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>7090000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>1974000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
+          <t>Bahor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>257402187</t>
+          <t>388670757</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000921132739001</t>
+          <t>20208000997006490001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №283/26</t>
+          <t>Предоплата за товар по договору №105/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
@@ -2595,21 +2595,21 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>9812000</v>
+        <v>1181000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Bahor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>388670757</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000997006490001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2619,14 +2619,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №273/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №5175 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2636,38 +2636,38 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>2585000</v>
+        <v>45112000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sharq Plastik MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>267355019</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000978552253001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №108/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №8923 от 04.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2675,40 +2675,40 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>4076000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>1495000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qo'qon Un Mahsulotlari MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>398736330</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000641574555001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5929</t>
+          <t>Оплата по счет-фактуре №8170 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2717,22 +2717,22 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>6715000</v>
+        <v>68599000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Qo'qon Un Mahsulotlari MChJ</t>
+          <t>Guliston Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>398736330</t>
+          <t>201599359</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000641574555001</t>
+          <t>20208000587134396001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2742,14 +2742,14 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №70/26 от 03.08.2026, НДС 12%</t>
+          <t>Оплата за сырье по договору №74/26 от 04.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2757,40 +2757,40 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>17143000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>3347000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>257402187</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000921132739001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3923</t>
+          <t>Оплата за продукцию по дог. №62/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2800,38 +2800,38 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>6980000</v>
+        <v>4223000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4777 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №48/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2860,14 +2860,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №9270</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №4168</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2875,23 +2875,23 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>16639000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>4071000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
+          <t>Afrosiyob Non MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>257402187</t>
+          <t>338086761</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000921132739001</t>
+          <t>20208000188311188001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2901,14 +2901,14 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №168/26</t>
+          <t>Предоплата за товар по договору №236/26 от 10.08.2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2918,38 +2918,38 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>46077000</v>
+        <v>3225000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №131/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №210/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2959,21 +2959,21 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>14253000</v>
+        <v>2232000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz XK</t>
+          <t>Shodlik Mebel MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>386833013</t>
+          <t>335501999</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000273604208001</t>
+          <t>20208000855225308001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2983,14 +2983,14 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7956 06.08.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3611</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3000,38 +3000,38 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>6054000</v>
+        <v>1870000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz XK</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>386833013</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000273604208001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Предолата за товар по договору №40/26 от 06.08.2026</t>
+          <t>Оплата за товар по счет-фактуре №1252 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3039,40 +3039,40 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>3163000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>1577000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Chust Qurilish MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>388102280</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000824216117001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №244/26 от 06.08.2026</t>
+          <t>Арендная плата за август 2026 г. по договору №57/25</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3080,40 +3080,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>1449000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>13501000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Shartnoma №93/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №190/26 от 10.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>15.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3121,40 +3121,35 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>1232000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>13700000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>215886707</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-1139)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000749970064001</t>
+          <t>16307000397310639417</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №728 от 06.08.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-1139 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3162,40 +3157,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>4995000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>4388000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nukus Poligraf XK</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>399652300</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000507586428001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №223/26 от 06.08.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4053</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3205,38 +3200,38 @@
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>2301000</v>
+        <v>2053000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9455 от 07.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №50/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3244,40 +3239,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>11974000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>1194000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №174/26, QQS 12%</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3286,39 +3281,39 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>1577000</v>
+        <v>1194000</v>
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>249052323</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000327831328001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №48/23</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3326,40 +3321,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>16044000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>9397000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7809 от 11.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №1358</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3367,23 +3362,23 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>2545000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>16066000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Olmaliq Moy MChJ</t>
+          <t>Zarafshon Logistik AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>312449034</t>
+          <t>252323532</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000631828552001</t>
+          <t>20208000831328400001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3393,14 +3388,14 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №190/26 ОТ 11.08.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №175/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3408,40 +3403,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>1907000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>39732000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sharq Plastik MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>267355019</t>
+          <t>397943825</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000978552253001</t>
+          <t>20208000533605331001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №171/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №225/26</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>15.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3449,35 +3444,40 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>13700000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>5099000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-1139)</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>16307000397310639417</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-1139 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за товар по счет-фактуре №4363 от 18.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3487,38 +3487,38 @@
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>26825000</v>
+        <v>3762000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №286/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №2966 18.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,40 +3526,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>1194000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>2614000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Оплата за продукцию по договору №247/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3567,40 +3567,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>1194000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>2238000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Оплата по счет-фактуре №2539 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3608,23 +3608,23 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>3016000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>1373000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3634,14 +3634,14 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9388</t>
+          <t>Оплата за продукцию по договору №195/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,23 +3649,23 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>3262000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>3913000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3675,14 +3675,14 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4876</t>
+          <t>Оплата за товар по счет-фактуре №3729 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3690,40 +3690,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>32957000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>2616000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nukus Poligraf XK</t>
+          <t>Bahor Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>399652300</t>
+          <t>201522288</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000507586428001</t>
+          <t>20208000754381728001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6102</t>
+          <t>Оплата за продукцию по договору №47/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,38 +3733,38 @@
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>9512000</v>
+        <v>2169000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №156/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №9532 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3774,38 +3774,38 @@
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>2842000</v>
+        <v>19089000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Olmaliq Tekstil MChJ</t>
+          <t>Durdona Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>205380867</t>
+          <t>217611357</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000191883111001</t>
+          <t>20208000292055988001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2820 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №2327 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3815,38 +3815,38 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>1365000</v>
+        <v>6702000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №221/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №2590 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3855,39 +3855,39 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>12365000</v>
+        <v>2630000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Qo'qon Un Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>398736330</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000641574555001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №60/26</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,23 +3895,23 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>3392000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>10483000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>397943825</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000533605331001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №298/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №118/26</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3938,38 +3938,38 @@
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>7995000</v>
+        <v>4164000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Nukus Agro XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>383301382</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000360420837001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Shartnoma №78/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №52/26 от 25.08.2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3979,38 +3979,38 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>11619000</v>
+        <v>2670000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Urganch Qurilish MChJ</t>
+          <t>Nukus Agro XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>265908551</t>
+          <t>383301382</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000280363276001</t>
+          <t>20208000360420837001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9883 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №851 от 25.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4020,38 +4020,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>6310000</v>
+        <v>1176000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №176/26, QQS 12%</t>
+          <t>Shartnoma №149/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4061,38 +4061,38 @@
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>1750000</v>
+        <v>1155000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Navro'z Tur Servis XK</t>
+          <t>Jizzax Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>315057106</t>
+          <t>365230045</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000884317090001</t>
+          <t>20208000758642853001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3608 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №3579 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4100,40 +4100,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>1716000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>16921000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №207/26 от 24.08.2026</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО С/Ф №2765</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4141,40 +4141,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>2557000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>49794000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Shartnoma №182/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4182,40 +4182,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>27168000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>1465000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
+          <t>Bahor Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>257402187</t>
+          <t>201522288</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000921132739001</t>
+          <t>20208000754381728001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №194/26 ОТ 24.08.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №1543 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,23 +4223,23 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>2505000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>985000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Navro'z Tur Servis XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>315057106</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000884317090001</t>
+          <t>20208000883060321001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №239/26 от 25.08.2026</t>
+          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4266,38 +4266,38 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>1481000</v>
+        <v>2015000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №241/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №5922 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4305,40 +4305,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>16628000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>15389000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Barakali Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>399250226</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000128787218001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №139/26</t>
+          <t>SHARTNOMA №91/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4346,40 +4346,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>985000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>10200000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000001784401001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата по счет-фактуре №2555 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4387,23 +4387,23 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>11750000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>2935000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4413,14 +4413,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6501</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7718 31.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4428,40 +4428,40 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>5429000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>2088000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Qo'qon Un Mahsulotlari MChJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>398736330</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000641574555001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №126/26</t>
+          <t>Оплата за продукцию по договору №268/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,23 +4469,23 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>11562000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>1362000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГ. №214/26 ОТ 28.08.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3094 31.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -4510,23 +4510,18 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>9366000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>311312733</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4536,7 +4531,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №174/26, НДС 12%</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
         </is>
       </c>
     </row>
@@ -4552,34 +4547,39 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>300000</v>
+        <v>9446000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Zarafshon Logistik AJ</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>252323532</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000831328400001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №283/26</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4587,40 +4587,40 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>4221000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>5443000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Qo'qon Un Mahsulotlari MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>398736330</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000641574555001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №80/26</t>
+          <t>Предплата за товар по дог. №63/26 от 01.09.2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4629,22 +4629,22 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>8212000</v>
+        <v>33028000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4654,14 +4654,14 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №284/26</t>
+          <t>Предоплата за материалы по договору №208/26</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4669,33 +4669,33 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>6798000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>6118000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>257402187</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000921132739001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №92/26</t>
+          <t>Оплата за товар по счет-фактуре №9185 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -4712,31 +4712,31 @@
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>26427000</v>
+        <v>3699000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №886 от 03.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5025 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -4751,23 +4751,23 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>30393000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>24660000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>397943825</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000533605331001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №261/26 от 04.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №8709</t>
         </is>
       </c>
     </row>
@@ -4794,31 +4794,31 @@
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>1755000</v>
+        <v>31486000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №188/26 от 07.09.2026</t>
+          <t>Предоплата за товар по дог. №159/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
@@ -4833,28 +4833,33 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>8966000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>7000000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Предоплата за товар по договору №36/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
@@ -4869,23 +4874,23 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>13289000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>5120000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4895,7 +4900,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2448</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3060 07.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -4911,32 +4916,32 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>21633000</v>
+        <v>1614000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
+          <t>Chust Qurilish MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>257402187</t>
+          <t>388102280</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000921132739001</t>
+          <t>20208000824216117001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №257/26, QQS bilan</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №57/25</t>
         </is>
       </c>
     </row>
@@ -4952,39 +4957,34 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>33048000</v>
+        <v>8966000</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Qo'qon Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>398736330</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000641574555001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6642</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4992,40 +4992,40 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>1614000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>12160000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari XK</t>
+          <t>Nukus Agro XK</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>249052323</t>
+          <t>383301382</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000327831328001</t>
+          <t>20208000360420837001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>BINO IJARASI UCHUN TO'LOV SENTYABR</t>
+          <t>Оплата за товар по с/ф №9369 от 10.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5033,40 +5033,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>3782000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>7171000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>257402187</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000921132739001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №161/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №574</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5076,38 +5076,38 @@
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>1410000</v>
+        <v>6853000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8457 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №5255 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5115,33 +5115,33 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>11932000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>6557000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>257402187</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000921132739001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №31/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4464 14.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -5158,31 +5158,31 @@
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>3999000</v>
+        <v>3405000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4875 за поставленный товар</t>
+          <t>Оплата по с/ф №8330 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -5198,39 +5198,39 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>9922000</v>
+        <v>1223000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8942</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5264,14 +5264,14 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5280,32 +5280,32 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>1223000</v>
+        <v>9108000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Оплата за товары согласно счет-фактуре №5572</t>
         </is>
       </c>
     </row>
@@ -5321,39 +5321,34 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>5091000</v>
+        <v>13700000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>257402187</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-1139)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000921132739001</t>
+          <t>16307000397310639417</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №47/26</t>
+          <t>Kredit shartnomasi L-2025-1139 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5362,34 +5357,39 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>13700000</v>
+        <v>6853000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-1139)</t>
+          <t>Marg'ilon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>16307000397310639417</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-1139 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за упаковочные материалы, с/ф №6324</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5399,21 +5399,21 @@
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>3938000</v>
+        <v>14654000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Bahor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>388670757</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000997006490001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5423,14 +5423,14 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9903 от 16.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №296/26 от 21.09.2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5440,38 +5440,38 @@
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>2435000</v>
+        <v>9752000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №682 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №1709 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5479,40 +5479,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>5137000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>2615000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Shartnoma №229/26 bo'yicha oldindan to'lov</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5521,39 +5521,39 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>5360000</v>
+        <v>16279000</v>
       </c>
       <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Nukus Poligraf XK</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>399652300</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000507586428001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №172/26</t>
+          <t>Предоплата за материалы по договору №171/26</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5561,40 +5561,40 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>1548000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>8920000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Olmaliq Moy MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>312449034</t>
+          <t>397943825</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000631828552001</t>
+          <t>20208000533605331001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Shartnoma №98/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №96/26</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5602,23 +5602,23 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>47674000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>25676000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>397943825</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000533605331001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №87/26 от 21.09.2026</t>
+          <t>Оплата за сырье по договору №136/26 от 22.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5645,21 +5645,21 @@
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>14263000</v>
+        <v>8907000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Bahor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>388670757</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000997006490001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5669,14 +5669,14 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №11/26 от 21.09.2026</t>
+          <t>ОПЛАТА ПО С/Ф №6276 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5686,38 +5686,38 @@
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>1605000</v>
+        <v>4981000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Navro'z Tur Servis XK</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>315057106</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000884317090001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №642 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товар по с/ф №8200 от 24.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5726,39 +5726,39 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>2739000</v>
+        <v>1009000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000883060321001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5766,40 +5766,40 @@
           <t>228</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>19611000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>8988000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Saodat Savdo MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>319909946</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000315222497001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Shartnoma №174/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №160/26</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5809,38 +5809,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>13996000</v>
+        <v>7286000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>ОПЛАТ ЗА ПРОДУКЦИЮ ПО ДОГ. №265/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6250 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5850,38 +5850,38 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>9001000</v>
+        <v>14390000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №41/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №7115 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5891,21 +5891,21 @@
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>3667000</v>
+        <v>14079000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Olmaliq Moy MChJ</t>
+          <t>Shodlik Mebel MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>312449034</t>
+          <t>335501999</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000631828552001</t>
+          <t>20208000855225308001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5915,14 +5915,14 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Shartnoma №106/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №269/26 от 28.09.2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5930,40 +5930,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>8570000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>9139000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Bahor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>388670757</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000997006490001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №173/26</t>
+          <t>Tovar uchun to'lov, h/f №1184 28.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5971,23 +5971,23 @@
           <t>233</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>11795000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>7758000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>209992502</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000601287872001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5997,14 +5997,14 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2914</t>
+          <t>Оплата по счет-фактуре №933 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6012,33 +6012,33 @@
           <t>234</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>13139000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>2619000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Nukus Poligraf XK</t>
+          <t>Sarbon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>399652300</t>
+          <t>390994633</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000507586428001</t>
+          <t>20208000522249734001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №72/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5624</t>
         </is>
       </c>
     </row>
@@ -6053,33 +6053,33 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>17869000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>5638000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish Materiallari MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>215886707</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000749970064001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №626 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №5757</t>
         </is>
       </c>
     </row>
@@ -6094,40 +6094,40 @@
           <t>236</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>8016000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>46933000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Marg'ilon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>340218789</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000113273987001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №215/26 от 28.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №1034</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6137,38 +6137,38 @@
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>4093000</v>
+        <v>29301000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>311312733</t>
+          <t>231273348</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000821531308001</t>
+          <t>20208000153130823001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №997 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №8029 от 30.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6176,300 +6176,54 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>2966000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>215886707</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000749970064001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №277/26 от 28.09.2026</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>2623000</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Olmaliq Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>205380867</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>20208000191883111001</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Shartnoma №198/26 bo'yicha oldindan to'lov</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>643486000</v>
+      </c>
+      <c r="D149" s="4" t="n">
+        <v>648186000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>1684000</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Farovon Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>311312733</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>20208000821531308001</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №95/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="n">
-        <v>1009000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>20208000001784401001</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию согласно счету</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>43737000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Oydin Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>209992502</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000601287872001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №31/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>4151000</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Farovon Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>311312733</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>20208000821531308001</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №148/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Zarafshon Kredit Bank</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="n">
-        <v>649534000</v>
-      </c>
-      <c r="D155" s="4" t="n">
-        <v>654234000</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C156" s="4" t="n">
+      <c r="C150" s="4" t="n">
         <v>76100000</v>
       </c>
-      <c r="D156" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
